--- a/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T14:55:17+00:00</t>
+    <t>2023-12-11T15:07:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Observation du Périmètre Crânien</t>
+    <t>Profil de la ressource Observation pour définir un Périmètre Crânien</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T15:07:49+00:00</t>
+    <t>2023-12-11T15:09:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T15:09:19+00:00</t>
+    <t>2023-12-11T15:13:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T15:13:34+00:00</t>
+    <t>2023-12-11T15:58:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -667,8 +667,7 @@
     <t>Motif de la mesure</t>
   </si>
   <si>
-    <t>Motif de la mesure
-Texte libre (ex. diabète, surpoids, maladie du cœur et des vaisseaux, cholestérol…)</t>
+    <t>Extension du Motif de la mesure, exprimé en texte libre  (ex. diabète, surpoids, maladie du cœur et des vaisseaux, cholestérol…).</t>
   </si>
   <si>
     <t>Observation.modifierExtension</t>

--- a/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T15:58:18+00:00</t>
+    <t>2023-12-11T16:02:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T16:02:47+00:00</t>
+    <t>2023-12-11T17:03:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$80</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3574" uniqueCount="661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3113" uniqueCount="639">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T17:03:26+00:00</t>
+    <t>2023-12-12T13:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1128,73 +1128,6 @@
   </si>
   <si>
     <t>116680003 |Is a|</t>
-  </si>
-  <si>
-    <t>Observation.code.id</t>
-  </si>
-  <si>
-    <t>Observation.code.extension</t>
-  </si>
-  <si>
-    <t>Observation.code.coding</t>
-  </si>
-  <si>
-    <t>value:code}
-value:system}</t>
-  </si>
-  <si>
-    <t>Observation.code.coding:headCircumCode</t>
-  </si>
-  <si>
-    <t>headCircumCode</t>
-  </si>
-  <si>
-    <t>Observation.code.coding:headCircumCode.id</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.code.coding:headCircumCode.extension</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.code.coding:headCircumCode.system</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.system</t>
-  </si>
-  <si>
-    <t>http://loinc.org</t>
-  </si>
-  <si>
-    <t>Observation.code.coding:headCircumCode.version</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.version</t>
-  </si>
-  <si>
-    <t>Observation.code.coding:headCircumCode.code</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.code</t>
-  </si>
-  <si>
-    <t>Observation.code.coding:headCircumCode.display</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.display</t>
-  </si>
-  <si>
-    <t>Observation.code.coding:headCircumCode.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.code.text</t>
   </si>
   <si>
     <t>Observation.subject</t>
@@ -2400,10 +2333,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP92"/>
+  <dimension ref="A1:AP80"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="52.83984375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="48.36328125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="27.03125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
@@ -7043,31 +6976,35 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>109</v>
+        <v>358</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>110</v>
+        <v>359</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
       </c>
@@ -7115,7 +7052,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>112</v>
+        <v>357</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7124,25 +7061,25 @@
         <v>93</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>82</v>
+        <v>230</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>82</v>
+        <v>363</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>82</v>
+        <v>364</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>113</v>
+        <v>365</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>82</v>
+        <v>366</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>82</v>
@@ -7150,14 +7087,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7173,19 +7110,19 @@
         <v>82</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>116</v>
+        <v>368</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>117</v>
+        <v>369</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>118</v>
+        <v>370</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>119</v>
+        <v>371</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7223,19 +7160,19 @@
         <v>82</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>123</v>
+        <v>367</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7247,7 +7184,7 @@
         <v>105</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>124</v>
+        <v>230</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -7256,13 +7193,13 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>82</v>
+        <v>353</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>107</v>
+        <v>372</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>82</v>
+        <v>366</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>82</v>
@@ -7270,21 +7207,21 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>82</v>
+        <v>374</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G41" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="G41" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -7296,19 +7233,19 @@
         <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>149</v>
+        <v>375</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>276</v>
+        <v>376</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>277</v>
+        <v>377</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>278</v>
+        <v>378</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>279</v>
+        <v>379</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -7345,44 +7282,46 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="AC41" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>280</v>
+        <v>373</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>106</v>
+        <v>230</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>82</v>
+        <v>380</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>281</v>
+        <v>381</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>282</v>
+        <v>382</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>82</v>
+        <v>383</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>82</v>
@@ -7390,16 +7329,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>361</v>
+        <v>384</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="C42" t="s" s="2">
-        <v>362</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>82</v>
+        <v>385</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7409,7 +7346,7 @@
         <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>82</v>
@@ -7418,19 +7355,19 @@
         <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>149</v>
+        <v>386</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>276</v>
+        <v>387</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>277</v>
+        <v>388</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>278</v>
+        <v>389</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>279</v>
+        <v>390</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7479,34 +7416,34 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>280</v>
+        <v>384</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>105</v>
+        <v>391</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>106</v>
+        <v>392</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>82</v>
+        <v>393</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>281</v>
+        <v>394</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>282</v>
+        <v>395</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>82</v>
+        <v>396</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>82</v>
@@ -7514,10 +7451,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>363</v>
+        <v>397</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>364</v>
+        <v>397</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7537,18 +7474,20 @@
         <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>110</v>
+        <v>398</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>400</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7597,7 +7536,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>112</v>
+        <v>397</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7606,10 +7545,10 @@
         <v>93</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
@@ -7618,13 +7557,13 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>82</v>
+        <v>401</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>113</v>
+        <v>402</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>82</v>
+        <v>403</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>82</v>
@@ -7632,14 +7571,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>365</v>
+        <v>404</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>366</v>
+        <v>404</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7655,21 +7594,23 @@
         <v>82</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>116</v>
+        <v>405</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>117</v>
+        <v>406</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>118</v>
+        <v>407</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>408</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7705,19 +7646,19 @@
         <v>82</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>123</v>
+        <v>404</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7729,22 +7670,22 @@
         <v>105</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>124</v>
+        <v>230</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>82</v>
+        <v>409</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>82</v>
+        <v>410</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>107</v>
+        <v>411</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>82</v>
+        <v>412</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>82</v>
@@ -7752,10 +7693,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>367</v>
+        <v>413</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>368</v>
+        <v>413</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7763,13 +7704,13 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>82</v>
@@ -7778,19 +7719,19 @@
         <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>137</v>
+        <v>414</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>289</v>
+        <v>415</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>290</v>
+        <v>415</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>291</v>
+        <v>416</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>292</v>
+        <v>417</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7800,7 +7741,7 @@
         <v>82</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>369</v>
+        <v>82</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>82</v>
@@ -7839,7 +7780,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>294</v>
+        <v>413</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7848,7 +7789,7 @@
         <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>105</v>
+        <v>418</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>106</v>
@@ -7857,27 +7798,27 @@
         <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>82</v>
+        <v>419</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>295</v>
+        <v>420</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>296</v>
+        <v>421</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>82</v>
+        <v>422</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>370</v>
+        <v>423</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>371</v>
+        <v>423</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7897,20 +7838,18 @@
         <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
         <v>109</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>299</v>
+        <v>110</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>301</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7959,7 +7898,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>302</v>
+        <v>112</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7968,10 +7907,10 @@
         <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -7980,10 +7919,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>303</v>
+        <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>304</v>
+        <v>113</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7994,21 +7933,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>372</v>
+        <v>424</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>373</v>
+        <v>424</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>82</v>
@@ -8017,23 +7956,21 @@
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>173</v>
+        <v>116</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>307</v>
+        <v>117</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>308</v>
+        <v>118</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>310</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
@@ -8069,31 +8006,31 @@
         <v>82</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>312</v>
+        <v>123</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
@@ -8102,10 +8039,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>313</v>
+        <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>314</v>
+        <v>107</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -8116,10 +8053,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>374</v>
+        <v>425</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8127,7 +8064,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>93</v>
@@ -8142,19 +8079,19 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>109</v>
+        <v>426</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>317</v>
+        <v>427</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>318</v>
+        <v>428</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>309</v>
+        <v>429</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>319</v>
+        <v>430</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -8203,7 +8140,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>320</v>
+        <v>431</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8224,10 +8161,10 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>321</v>
+        <v>432</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>322</v>
+        <v>433</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -8238,10 +8175,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>376</v>
+        <v>434</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>377</v>
+        <v>434</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8258,30 +8195,32 @@
         <v>82</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J49" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>325</v>
+        <v>173</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>326</v>
+        <v>435</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>327</v>
+        <v>436</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>328</v>
+        <v>309</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>329</v>
+        <v>437</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q49" s="2"/>
+      <c r="Q49" t="s" s="2">
+        <v>438</v>
+      </c>
       <c r="R49" t="s" s="2">
         <v>82</v>
       </c>
@@ -8301,13 +8240,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>82</v>
+        <v>248</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>82</v>
+        <v>439</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>82</v>
+        <v>440</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -8325,7 +8264,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>330</v>
+        <v>441</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8346,10 +8285,10 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>331</v>
+        <v>442</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>332</v>
+        <v>443</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8360,10 +8299,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>378</v>
+        <v>444</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>378</v>
+        <v>444</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8371,7 +8310,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>93</v>
@@ -8389,16 +8328,16 @@
         <v>109</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>335</v>
+        <v>445</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>336</v>
+        <v>446</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>337</v>
+        <v>309</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>338</v>
+        <v>447</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8408,7 +8347,7 @@
         <v>82</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>82</v>
+        <v>448</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>82</v>
@@ -8447,7 +8386,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>339</v>
+        <v>449</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8468,10 +8407,10 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>340</v>
+        <v>450</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>341</v>
+        <v>451</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8482,10 +8421,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>379</v>
+        <v>452</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>379</v>
+        <v>452</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8493,13 +8432,13 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>82</v>
@@ -8508,19 +8447,19 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>380</v>
+        <v>137</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>381</v>
+        <v>453</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>382</v>
+        <v>454</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>383</v>
+        <v>455</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>384</v>
+        <v>456</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8530,7 +8469,7 @@
         <v>82</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>82</v>
+        <v>457</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>82</v>
@@ -8569,7 +8508,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>379</v>
+        <v>458</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8578,25 +8517,25 @@
         <v>93</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>105</v>
+        <v>459</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>230</v>
+        <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>385</v>
+        <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>386</v>
+        <v>450</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>387</v>
+        <v>460</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>388</v>
+        <v>82</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>
@@ -8604,10 +8543,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>389</v>
+        <v>461</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>389</v>
+        <v>461</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8615,10 +8554,10 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
@@ -8630,18 +8569,20 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>390</v>
+        <v>173</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>391</v>
+        <v>462</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>392</v>
+        <v>463</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>464</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>465</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
@@ -8689,19 +8630,19 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>389</v>
+        <v>466</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>230</v>
+        <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
@@ -8710,13 +8651,13 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>353</v>
+        <v>450</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>394</v>
+        <v>467</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>388</v>
+        <v>82</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8724,14 +8665,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>395</v>
+        <v>468</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>395</v>
+        <v>468</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>396</v>
+        <v>82</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8741,28 +8682,28 @@
         <v>93</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>397</v>
+        <v>257</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>398</v>
+        <v>469</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>399</v>
+        <v>470</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>400</v>
+        <v>471</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>401</v>
+        <v>472</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8787,13 +8728,13 @@
         <v>82</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>82</v>
+        <v>153</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>82</v>
+        <v>473</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>82</v>
+        <v>474</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>82</v>
@@ -8811,7 +8752,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>395</v>
+        <v>468</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8820,25 +8761,25 @@
         <v>93</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>105</v>
+        <v>475</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>230</v>
+        <v>106</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>402</v>
+        <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>403</v>
+        <v>107</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>404</v>
+        <v>476</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>405</v>
+        <v>82</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -8846,45 +8787,45 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>406</v>
+        <v>477</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>406</v>
+        <v>477</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>407</v>
+        <v>478</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>408</v>
+        <v>257</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>409</v>
+        <v>479</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>410</v>
+        <v>480</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>411</v>
+        <v>481</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>412</v>
+        <v>482</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8909,13 +8850,13 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>82</v>
+        <v>153</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>82</v>
+        <v>483</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>82</v>
+        <v>484</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -8933,45 +8874,45 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>406</v>
+        <v>477</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>413</v>
+        <v>105</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>414</v>
+        <v>106</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>415</v>
+        <v>82</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>82</v>
+        <v>485</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>416</v>
+        <v>486</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>417</v>
+        <v>487</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>418</v>
+        <v>82</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>82</v>
+        <v>488</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>419</v>
+        <v>489</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>419</v>
+        <v>489</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8982,7 +8923,7 @@
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -8991,21 +8932,23 @@
         <v>82</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>131</v>
+        <v>490</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>420</v>
+        <v>491</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>421</v>
+        <v>492</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>493</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>494</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
       </c>
@@ -9053,13 +8996,13 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>419</v>
+        <v>489</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>105</v>
@@ -9074,13 +9017,13 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>423</v>
+        <v>495</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>424</v>
+        <v>496</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>425</v>
+        <v>82</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
@@ -9088,10 +9031,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>426</v>
+        <v>497</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>426</v>
+        <v>497</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9102,7 +9045,7 @@
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>82</v>
@@ -9111,23 +9054,21 @@
         <v>82</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>427</v>
+        <v>257</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>428</v>
+        <v>498</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>429</v>
+        <v>499</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>430</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>82</v>
       </c>
@@ -9151,13 +9092,13 @@
         <v>82</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>82</v>
+        <v>501</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>82</v>
+        <v>502</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>82</v>
@@ -9175,45 +9116,45 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>426</v>
+        <v>497</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>230</v>
+        <v>106</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>431</v>
+        <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>82</v>
+        <v>503</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>432</v>
+        <v>504</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>433</v>
+        <v>505</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>434</v>
+        <v>82</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>82</v>
+        <v>506</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>435</v>
+        <v>507</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>435</v>
+        <v>507</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9227,28 +9168,28 @@
         <v>93</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>436</v>
+        <v>257</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>437</v>
+        <v>508</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>437</v>
+        <v>509</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>438</v>
+        <v>510</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>439</v>
+        <v>511</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -9273,13 +9214,13 @@
         <v>82</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>82</v>
+        <v>512</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>82</v>
+        <v>513</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
@@ -9297,7 +9238,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>435</v>
+        <v>507</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9306,7 +9247,7 @@
         <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>440</v>
+        <v>105</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>106</v>
@@ -9315,27 +9256,27 @@
         <v>82</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>441</v>
+        <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>442</v>
+        <v>514</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>443</v>
+        <v>515</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>444</v>
+        <v>82</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>445</v>
+        <v>516</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>445</v>
+        <v>516</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9358,15 +9299,17 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>109</v>
+        <v>517</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>110</v>
+        <v>518</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>519</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>520</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9415,7 +9358,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>112</v>
+        <v>516</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9424,47 +9367,47 @@
         <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>82</v>
+        <v>230</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>82</v>
+        <v>521</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>82</v>
+        <v>522</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>113</v>
+        <v>523</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>82</v>
+        <v>524</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>446</v>
+        <v>525</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>446</v>
+        <v>525</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>82</v>
@@ -9476,16 +9419,16 @@
         <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>116</v>
+        <v>526</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>117</v>
+        <v>527</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>118</v>
+        <v>528</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>119</v>
+        <v>529</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9523,57 +9466,57 @@
         <v>82</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>123</v>
+        <v>525</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>124</v>
+        <v>230</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>82</v>
+        <v>530</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>82</v>
+        <v>531</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>107</v>
+        <v>532</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>82</v>
+        <v>533</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>447</v>
+        <v>534</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>447</v>
+        <v>534</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9581,10 +9524,10 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
@@ -9593,22 +9536,22 @@
         <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>448</v>
+        <v>535</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>449</v>
+        <v>536</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>450</v>
+        <v>537</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>451</v>
+        <v>538</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>452</v>
+        <v>539</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9657,19 +9600,19 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>453</v>
+        <v>534</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>106</v>
+        <v>540</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
@@ -9678,10 +9621,10 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>454</v>
+        <v>541</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>455</v>
+        <v>542</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9692,10 +9635,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>456</v>
+        <v>543</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>456</v>
+        <v>543</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9712,32 +9655,26 @@
         <v>82</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>173</v>
+        <v>109</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>457</v>
+        <v>110</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>459</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q61" t="s" s="2">
-        <v>460</v>
-      </c>
+      <c r="Q61" s="2"/>
       <c r="R61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9757,13 +9694,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>248</v>
+        <v>82</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>461</v>
+        <v>82</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>462</v>
+        <v>82</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9781,7 +9718,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>463</v>
+        <v>112</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9790,10 +9727,10 @@
         <v>93</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
@@ -9802,10 +9739,10 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>464</v>
+        <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>465</v>
+        <v>113</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9816,21 +9753,21 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>466</v>
+        <v>544</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>466</v>
+        <v>544</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -9839,23 +9776,21 @@
         <v>82</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>467</v>
+        <v>117</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>468</v>
+        <v>118</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>469</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9864,7 +9799,7 @@
         <v>82</v>
       </c>
       <c r="S62" t="s" s="2">
-        <v>470</v>
+        <v>82</v>
       </c>
       <c r="T62" t="s" s="2">
         <v>82</v>
@@ -9891,31 +9826,31 @@
         <v>82</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>471</v>
+        <v>123</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>82</v>
@@ -9924,10 +9859,10 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>472</v>
+        <v>82</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>473</v>
+        <v>107</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9938,45 +9873,45 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>474</v>
+        <v>545</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>474</v>
+        <v>545</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>82</v>
+        <v>546</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J63" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>475</v>
+        <v>547</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>476</v>
+        <v>548</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>477</v>
+        <v>119</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>478</v>
+        <v>212</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9986,7 +9921,7 @@
         <v>82</v>
       </c>
       <c r="S63" t="s" s="2">
-        <v>479</v>
+        <v>82</v>
       </c>
       <c r="T63" t="s" s="2">
         <v>82</v>
@@ -10025,19 +9960,19 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>480</v>
+        <v>549</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>481</v>
+        <v>105</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>82</v>
@@ -10046,10 +9981,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>472</v>
+        <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>482</v>
+        <v>107</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -10060,10 +9995,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>483</v>
+        <v>550</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>483</v>
+        <v>550</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10071,7 +10006,7 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>93</v>
@@ -10083,23 +10018,21 @@
         <v>82</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>173</v>
+        <v>551</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>484</v>
+        <v>552</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>485</v>
+        <v>553</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>487</v>
-      </c>
+        <v>554</v>
+      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>82</v>
       </c>
@@ -10147,7 +10080,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>488</v>
+        <v>550</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10156,10 +10089,10 @@
         <v>93</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>105</v>
+        <v>555</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>106</v>
+        <v>556</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>82</v>
@@ -10168,10 +10101,10 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>472</v>
+        <v>557</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>489</v>
+        <v>558</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -10182,10 +10115,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>490</v>
+        <v>559</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>490</v>
+        <v>559</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10199,7 +10132,7 @@
         <v>93</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>82</v>
@@ -10208,20 +10141,18 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>257</v>
+        <v>551</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>491</v>
+        <v>560</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>492</v>
+        <v>561</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>494</v>
-      </c>
+        <v>554</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
@@ -10245,13 +10176,13 @@
         <v>82</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>153</v>
+        <v>82</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>495</v>
+        <v>82</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>496</v>
+        <v>82</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>82</v>
@@ -10269,7 +10200,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>490</v>
+        <v>559</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10278,10 +10209,10 @@
         <v>93</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>497</v>
+        <v>555</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>106</v>
+        <v>556</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>82</v>
@@ -10290,10 +10221,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>107</v>
+        <v>557</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>498</v>
+        <v>562</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10304,21 +10235,21 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>499</v>
+        <v>563</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>499</v>
+        <v>563</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>500</v>
+        <v>82</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>82</v>
@@ -10333,16 +10264,16 @@
         <v>257</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>501</v>
+        <v>564</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>502</v>
+        <v>565</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>503</v>
+        <v>566</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>504</v>
+        <v>567</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -10367,13 +10298,13 @@
         <v>82</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>505</v>
+        <v>568</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>506</v>
+        <v>569</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>82</v>
@@ -10391,13 +10322,13 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>499</v>
+        <v>563</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>105</v>
@@ -10409,27 +10340,27 @@
         <v>82</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>507</v>
+        <v>570</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>508</v>
+        <v>571</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>509</v>
+        <v>487</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>510</v>
+        <v>82</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>511</v>
+        <v>572</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>511</v>
+        <v>572</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10452,19 +10383,19 @@
         <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>512</v>
+        <v>257</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>513</v>
+        <v>573</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>514</v>
+        <v>574</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>515</v>
+        <v>575</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>516</v>
+        <v>576</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10489,13 +10420,13 @@
         <v>82</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>82</v>
+        <v>577</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>82</v>
+        <v>578</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -10513,7 +10444,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>511</v>
+        <v>572</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10531,13 +10462,13 @@
         <v>82</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>82</v>
+        <v>570</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>517</v>
+        <v>571</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>518</v>
+        <v>487</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10548,10 +10479,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>519</v>
+        <v>579</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>519</v>
+        <v>579</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10574,18 +10505,20 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>257</v>
+        <v>580</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>520</v>
+        <v>581</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>521</v>
+        <v>582</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="O68" s="2"/>
+        <v>583</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>584</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
@@ -10609,13 +10542,13 @@
         <v>82</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>523</v>
+        <v>82</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>524</v>
+        <v>82</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
@@ -10633,7 +10566,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>519</v>
+        <v>579</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10645,33 +10578,33 @@
         <v>105</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>106</v>
+        <v>585</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>525</v>
+        <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>526</v>
+        <v>586</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>527</v>
+        <v>587</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>528</v>
+        <v>82</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>529</v>
+        <v>588</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>529</v>
+        <v>588</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10694,20 +10627,18 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>257</v>
+        <v>109</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>530</v>
+        <v>589</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>531</v>
+        <v>590</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>533</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>82</v>
       </c>
@@ -10731,13 +10662,13 @@
         <v>82</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>534</v>
+        <v>82</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>535</v>
+        <v>82</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -10755,7 +10686,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>529</v>
+        <v>588</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10776,10 +10707,10 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>536</v>
+        <v>557</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>537</v>
+        <v>591</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10790,10 +10721,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>538</v>
+        <v>592</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>538</v>
+        <v>592</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10804,7 +10735,7 @@
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>82</v>
@@ -10813,19 +10744,19 @@
         <v>82</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>539</v>
+        <v>593</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>540</v>
+        <v>594</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>541</v>
+        <v>595</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>542</v>
+        <v>596</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10875,13 +10806,13 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>538</v>
+        <v>592</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>105</v>
@@ -10893,27 +10824,27 @@
         <v>82</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>543</v>
+        <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>544</v>
+        <v>597</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>545</v>
+        <v>598</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>546</v>
+        <v>82</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>547</v>
+        <v>599</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>547</v>
+        <v>599</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10924,7 +10855,7 @@
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>82</v>
@@ -10933,19 +10864,19 @@
         <v>82</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>548</v>
+        <v>600</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>549</v>
+        <v>601</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>550</v>
+        <v>602</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>551</v>
+        <v>603</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10995,13 +10926,13 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>547</v>
+        <v>599</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>105</v>
@@ -11013,27 +10944,27 @@
         <v>82</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>552</v>
+        <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>553</v>
+        <v>597</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>554</v>
+        <v>604</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>555</v>
+        <v>82</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>556</v>
+        <v>605</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>556</v>
+        <v>605</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11047,28 +10978,28 @@
         <v>81</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>557</v>
+        <v>535</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>558</v>
+        <v>606</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>559</v>
+        <v>606</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>560</v>
+        <v>607</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>561</v>
+        <v>608</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>82</v>
@@ -11117,7 +11048,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>556</v>
+        <v>605</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11129,7 +11060,7 @@
         <v>105</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>562</v>
+        <v>609</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>82</v>
@@ -11138,10 +11069,10 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>563</v>
+        <v>610</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>564</v>
+        <v>611</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -11152,10 +11083,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>565</v>
+        <v>612</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>565</v>
+        <v>612</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11270,10 +11201,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>566</v>
+        <v>613</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>566</v>
+        <v>613</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11390,14 +11321,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>567</v>
+        <v>614</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>567</v>
+        <v>614</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>568</v>
+        <v>546</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -11419,10 +11350,10 @@
         <v>116</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>569</v>
+        <v>547</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>570</v>
+        <v>548</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>119</v>
@@ -11477,7 +11408,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>571</v>
+        <v>549</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11512,10 +11443,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>572</v>
+        <v>615</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>572</v>
+        <v>615</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11523,33 +11454,35 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>573</v>
+        <v>257</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>574</v>
+        <v>616</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>575</v>
+        <v>617</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="O76" s="2"/>
+        <v>618</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>619</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
       </c>
@@ -11573,13 +11506,13 @@
         <v>82</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>82</v>
+        <v>153</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>82</v>
+        <v>349</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>82</v>
+        <v>350</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>82</v>
@@ -11597,34 +11530,34 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>572</v>
+        <v>615</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>577</v>
+        <v>105</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>578</v>
+        <v>106</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>82</v>
+        <v>620</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>579</v>
+        <v>353</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>580</v>
+        <v>354</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>82</v>
+        <v>355</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>82</v>
@@ -11632,10 +11565,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>581</v>
+        <v>621</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>581</v>
+        <v>621</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11649,27 +11582,29 @@
         <v>93</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>573</v>
+        <v>622</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>582</v>
+        <v>623</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>583</v>
+        <v>624</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="O77" s="2"/>
+        <v>625</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>417</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
       </c>
@@ -11693,13 +11628,13 @@
         <v>82</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>82</v>
+        <v>248</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>82</v>
+        <v>626</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>82</v>
+        <v>627</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>82</v>
@@ -11717,7 +11652,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>581</v>
+        <v>621</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11726,36 +11661,36 @@
         <v>93</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>577</v>
+        <v>628</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>578</v>
+        <v>106</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>82</v>
+        <v>629</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>579</v>
+        <v>420</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>584</v>
+        <v>421</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>82</v>
+        <v>422</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>585</v>
+        <v>630</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>585</v>
+        <v>630</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11769,7 +11704,7 @@
         <v>93</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>82</v>
@@ -11781,16 +11716,16 @@
         <v>257</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>586</v>
+        <v>631</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>587</v>
+        <v>632</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>588</v>
+        <v>633</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>589</v>
+        <v>472</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11815,13 +11750,13 @@
         <v>82</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>590</v>
+        <v>473</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>591</v>
+        <v>474</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>82</v>
@@ -11839,7 +11774,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>585</v>
+        <v>630</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11848,7 +11783,7 @@
         <v>93</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>105</v>
+        <v>634</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>106</v>
@@ -11857,13 +11792,13 @@
         <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>592</v>
+        <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>593</v>
+        <v>107</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>509</v>
+        <v>476</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11874,14 +11809,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>594</v>
+        <v>635</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>594</v>
+        <v>635</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>82</v>
+        <v>478</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11903,16 +11838,16 @@
         <v>257</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>595</v>
+        <v>479</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>596</v>
+        <v>480</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>597</v>
+        <v>481</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>598</v>
+        <v>482</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -11937,13 +11872,13 @@
         <v>82</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>599</v>
+        <v>483</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>600</v>
+        <v>484</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>82</v>
@@ -11961,7 +11896,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>594</v>
+        <v>635</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11979,27 +11914,27 @@
         <v>82</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>592</v>
+        <v>485</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>593</v>
+        <v>486</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>509</v>
+        <v>487</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>82</v>
+        <v>488</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>601</v>
+        <v>636</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>601</v>
+        <v>636</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12010,7 +11945,7 @@
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>82</v>
@@ -12022,19 +11957,19 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>602</v>
+        <v>83</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>603</v>
+        <v>637</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>604</v>
+        <v>638</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>605</v>
+        <v>538</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>606</v>
+        <v>539</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -12083,19 +12018,19 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>601</v>
+        <v>636</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>607</v>
+        <v>82</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>82</v>
@@ -12104,1472 +12039,20 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>608</v>
+        <v>541</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>609</v>
+        <v>542</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="81" hidden="true">
-      <c r="A81" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="D81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E81" s="2"/>
-      <c r="F81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K81" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O81" s="2"/>
-      <c r="P81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q81" s="2"/>
-      <c r="R81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AJ81" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP81" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="82" hidden="true">
-      <c r="A82" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="C82" s="2"/>
-      <c r="D82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E82" s="2"/>
-      <c r="F82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J82" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K82" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="O82" s="2"/>
-      <c r="P82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q82" s="2"/>
-      <c r="R82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP82" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="83" hidden="true">
-      <c r="A83" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="C83" s="2"/>
-      <c r="D83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E83" s="2"/>
-      <c r="F83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K83" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="O83" s="2"/>
-      <c r="P83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q83" s="2"/>
-      <c r="R83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="AK83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP83" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="84" hidden="true">
-      <c r="A84" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="C84" s="2"/>
-      <c r="D84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E84" s="2"/>
-      <c r="F84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H84" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J84" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K84" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="L84" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="P84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q84" s="2"/>
-      <c r="R84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP84" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="85" hidden="true">
-      <c r="A85" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="C85" s="2"/>
-      <c r="D85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E85" s="2"/>
-      <c r="F85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G85" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K85" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L85" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
-      <c r="P85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q85" s="2"/>
-      <c r="R85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AG85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH85" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP85" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="86" hidden="true">
-      <c r="A86" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="C86" s="2"/>
-      <c r="D86" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="E86" s="2"/>
-      <c r="F86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K86" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="L86" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="O86" s="2"/>
-      <c r="P86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q86" s="2"/>
-      <c r="R86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="AG86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI86" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AJ86" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="AK86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AO86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP86" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="87" hidden="true">
-      <c r="A87" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="C87" s="2"/>
-      <c r="D87" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="E87" s="2"/>
-      <c r="F87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I87" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="J87" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K87" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="L87" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="P87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q87" s="2"/>
-      <c r="R87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="AG87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI87" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AJ87" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="AK87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AO87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP87" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="88" hidden="true">
-      <c r="A88" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="C88" s="2"/>
-      <c r="D88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E88" s="2"/>
-      <c r="F88" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="G88" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H88" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J88" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K88" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="L88" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="P88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q88" s="2"/>
-      <c r="R88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X88" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="AG88" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AH88" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI88" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AJ88" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="AO88" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="AP88" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="89" hidden="true">
-      <c r="A89" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="B89" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="C89" s="2"/>
-      <c r="D89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E89" s="2"/>
-      <c r="F89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G89" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H89" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J89" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K89" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="L89" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="P89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q89" s="2"/>
-      <c r="R89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X89" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="Y89" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="Z89" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="AA89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF89" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="AG89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH89" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI89" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="AJ89" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="AM89" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="AO89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP89" t="s" s="2">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="90" hidden="true">
-      <c r="A90" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="C90" s="2"/>
-      <c r="D90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E90" s="2"/>
-      <c r="F90" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G90" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H90" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K90" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="L90" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="P90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q90" s="2"/>
-      <c r="R90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X90" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="Z90" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="AG90" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH90" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI90" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="AJ90" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM90" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="AO90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP90" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="91" hidden="true">
-      <c r="A91" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="C91" s="2"/>
-      <c r="D91" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="E91" s="2"/>
-      <c r="F91" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K91" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="L91" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="P91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q91" s="2"/>
-      <c r="R91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X91" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="Z91" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="AG91" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI91" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AJ91" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL91" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP91" t="s" s="2">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="92" hidden="true">
-      <c r="A92" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="C92" s="2"/>
-      <c r="D92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E92" s="2"/>
-      <c r="F92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K92" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L92" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="P92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q92" s="2"/>
-      <c r="R92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="AG92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM92" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP92" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP92">
+  <autoFilter ref="A1:AP80">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13579,7 +12062,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI91">
+  <conditionalFormatting sqref="A2:AI79">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T13:44:55+00:00</t>
+    <t>2023-12-12T13:59:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$85</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3113" uniqueCount="639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3305" uniqueCount="646">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T13:59:44+00:00</t>
+    <t>2023-12-12T14:34:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1098,14 +1098,6 @@
     <t>5. SHALL contain exactly one [1..1] code, where the @code SHOULD be selected from ValueSet HITSP Vital Sign Result Type 2.16.840.1.113883.3.88.12.80.62 DYNAMIC (CONF:7301).</t>
   </si>
   <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://loinc.org"/&gt;
-    &lt;code value="8287-5"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
     <t>This identifies the vital sign result type.</t>
   </si>
   <si>
@@ -1128,6 +1120,34 @@
   </si>
   <si>
     <t>116680003 |Is a|</t>
+  </si>
+  <si>
+    <t>Observation.code.id</t>
+  </si>
+  <si>
+    <t>Observation.code.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding</t>
+  </si>
+  <si>
+    <t>value:code}
+value:system}</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:headCircumCode</t>
+  </si>
+  <si>
+    <t>headCircumCode</t>
+  </si>
+  <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="http://loinc.org"/&gt;
+  &lt;code value="8287-5"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
+    <t>Observation.code.text</t>
   </si>
   <si>
     <t>Observation.subject</t>
@@ -2333,7 +2353,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP80"/>
+  <dimension ref="A1:AP85"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="48.36328125" customWidth="true" bestFit="true"/>
@@ -6891,7 +6911,7 @@
         <v>82</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>82</v>
@@ -6909,10 +6929,10 @@
         <v>153</v>
       </c>
       <c r="Y38" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="Z38" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="Z38" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6945,30 +6965,30 @@
         <v>106</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AN38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AO38" t="s" s="2">
+      <c r="AP38" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>356</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6976,35 +6996,31 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>358</v>
+        <v>109</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>359</v>
+        <v>110</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>362</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>82</v>
       </c>
@@ -7052,7 +7068,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>357</v>
+        <v>112</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7061,25 +7077,25 @@
         <v>93</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>230</v>
+        <v>82</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>363</v>
+        <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>364</v>
+        <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>365</v>
+        <v>113</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>366</v>
+        <v>82</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>82</v>
@@ -7087,14 +7103,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7110,19 +7126,19 @@
         <v>82</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>368</v>
+        <v>116</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>369</v>
+        <v>117</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>370</v>
+        <v>118</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>371</v>
+        <v>119</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7160,19 +7176,19 @@
         <v>82</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>367</v>
+        <v>123</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7184,7 +7200,7 @@
         <v>105</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>230</v>
+        <v>124</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -7193,13 +7209,13 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>372</v>
+        <v>107</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>366</v>
+        <v>82</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>82</v>
@@ -7207,21 +7223,21 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>374</v>
+        <v>82</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -7233,19 +7249,19 @@
         <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>375</v>
+        <v>149</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>376</v>
+        <v>276</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>377</v>
+        <v>277</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>378</v>
+        <v>278</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>379</v>
+        <v>279</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -7282,46 +7298,44 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>373</v>
+        <v>280</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>230</v>
+        <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>380</v>
+        <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>381</v>
+        <v>281</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>382</v>
+        <v>282</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>383</v>
+        <v>82</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>82</v>
@@ -7329,14 +7343,16 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>384</v>
+        <v>360</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="C42" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="D42" t="s" s="2">
-        <v>385</v>
+        <v>82</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7346,7 +7362,7 @@
         <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>82</v>
@@ -7355,19 +7371,19 @@
         <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>386</v>
+        <v>149</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>387</v>
+        <v>276</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>388</v>
+        <v>277</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>389</v>
+        <v>278</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>390</v>
+        <v>279</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7377,7 +7393,7 @@
         <v>82</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>82</v>
+        <v>362</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>82</v>
@@ -7416,34 +7432,34 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>384</v>
+        <v>280</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>391</v>
+        <v>105</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>392</v>
+        <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>393</v>
+        <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>394</v>
+        <v>281</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>395</v>
+        <v>282</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>396</v>
+        <v>82</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>82</v>
@@ -7451,10 +7467,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>397</v>
+        <v>363</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>397</v>
+        <v>363</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7477,18 +7493,20 @@
         <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>398</v>
+        <v>335</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>399</v>
+        <v>336</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7536,7 +7554,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>397</v>
+        <v>339</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7557,13 +7575,13 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>401</v>
+        <v>340</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>402</v>
+        <v>341</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>403</v>
+        <v>82</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>82</v>
@@ -7571,10 +7589,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>404</v>
+        <v>364</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>404</v>
+        <v>364</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7582,13 +7600,13 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>82</v>
@@ -7597,19 +7615,19 @@
         <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>405</v>
+        <v>365</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>406</v>
+        <v>366</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>407</v>
+        <v>367</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>228</v>
+        <v>368</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>408</v>
+        <v>369</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7658,13 +7676,13 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>404</v>
+        <v>364</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>105</v>
@@ -7673,19 +7691,19 @@
         <v>230</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>409</v>
+        <v>370</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>410</v>
+        <v>371</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>411</v>
+        <v>372</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>412</v>
+        <v>373</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>82</v>
@@ -7693,10 +7711,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>413</v>
+        <v>374</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>413</v>
+        <v>374</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7707,10 +7725,10 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>82</v>
@@ -7719,20 +7737,18 @@
         <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>414</v>
+        <v>375</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>415</v>
+        <v>376</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>415</v>
+        <v>377</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7780,49 +7796,49 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>413</v>
+        <v>374</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>418</v>
+        <v>105</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>106</v>
+        <v>230</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>419</v>
+        <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>420</v>
+        <v>352</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>421</v>
+        <v>379</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>82</v>
+        <v>373</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>422</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>423</v>
+        <v>380</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>423</v>
+        <v>380</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>82</v>
+        <v>381</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7838,19 +7854,23 @@
         <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>109</v>
+        <v>382</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>110</v>
+        <v>383</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>384</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
@@ -7898,7 +7918,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>112</v>
+        <v>380</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7907,25 +7927,25 @@
         <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>82</v>
+        <v>230</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>82</v>
+        <v>388</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>113</v>
+        <v>389</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>82</v>
+        <v>390</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>82</v>
@@ -7933,44 +7953,46 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>424</v>
+        <v>391</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>424</v>
+        <v>391</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>115</v>
+        <v>392</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>116</v>
+        <v>393</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>117</v>
+        <v>394</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>118</v>
+        <v>395</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>397</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
@@ -8006,46 +8028,46 @@
         <v>82</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>123</v>
+        <v>391</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>105</v>
+        <v>398</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>124</v>
+        <v>399</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>82</v>
+        <v>400</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>82</v>
+        <v>401</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>107</v>
+        <v>402</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>82</v>
+        <v>403</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
@@ -8053,10 +8075,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>425</v>
+        <v>404</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>425</v>
+        <v>404</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8064,7 +8086,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>93</v>
@@ -8079,20 +8101,18 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>426</v>
+        <v>131</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>427</v>
+        <v>405</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>428</v>
+        <v>406</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>430</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
@@ -8140,7 +8160,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>431</v>
+        <v>404</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8161,13 +8181,13 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>432</v>
+        <v>408</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>433</v>
+        <v>409</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>82</v>
+        <v>410</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -8175,10 +8195,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>434</v>
+        <v>411</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>434</v>
+        <v>411</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8189,38 +8209,36 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J49" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>173</v>
+        <v>412</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>435</v>
+        <v>413</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>436</v>
+        <v>414</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>309</v>
+        <v>228</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>437</v>
+        <v>415</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q49" t="s" s="2">
-        <v>438</v>
-      </c>
+      <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
         <v>82</v>
       </c>
@@ -8240,13 +8258,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>248</v>
+        <v>82</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>439</v>
+        <v>82</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>440</v>
+        <v>82</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -8264,34 +8282,34 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>441</v>
+        <v>411</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>106</v>
+        <v>230</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>82</v>
+        <v>416</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>442</v>
+        <v>417</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>443</v>
+        <v>418</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>82</v>
+        <v>419</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -8299,10 +8317,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>444</v>
+        <v>420</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>444</v>
+        <v>420</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8310,13 +8328,13 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>82</v>
@@ -8325,19 +8343,19 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>109</v>
+        <v>421</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>445</v>
+        <v>422</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>446</v>
+        <v>422</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>309</v>
+        <v>423</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>447</v>
+        <v>424</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8347,7 +8365,7 @@
         <v>82</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>448</v>
+        <v>82</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>82</v>
@@ -8386,7 +8404,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>449</v>
+        <v>420</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8395,7 +8413,7 @@
         <v>93</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>105</v>
+        <v>425</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>106</v>
@@ -8404,27 +8422,27 @@
         <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>82</v>
+        <v>426</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>450</v>
+        <v>427</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>451</v>
+        <v>428</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>82</v>
+        <v>429</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>452</v>
+        <v>430</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>452</v>
+        <v>430</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8444,23 +8462,19 @@
         <v>82</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>453</v>
+        <v>110</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>456</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
@@ -8469,7 +8483,7 @@
         <v>82</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>457</v>
+        <v>82</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>82</v>
@@ -8508,7 +8522,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>458</v>
+        <v>112</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8517,10 +8531,10 @@
         <v>93</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>459</v>
+        <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>82</v>
@@ -8529,10 +8543,10 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>450</v>
+        <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>460</v>
+        <v>113</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8543,21 +8557,21 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>461</v>
+        <v>431</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>461</v>
+        <v>431</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
@@ -8566,23 +8580,21 @@
         <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>173</v>
+        <v>116</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>462</v>
+        <v>117</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>463</v>
+        <v>118</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>465</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
@@ -8618,31 +8630,31 @@
         <v>82</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>466</v>
+        <v>123</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
@@ -8651,10 +8663,10 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>450</v>
+        <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>467</v>
+        <v>107</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8665,10 +8677,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>468</v>
+        <v>432</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>468</v>
+        <v>432</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8676,34 +8688,34 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J53" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K53" t="s" s="2">
-        <v>257</v>
+        <v>433</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>469</v>
+        <v>434</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>470</v>
+        <v>435</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>471</v>
+        <v>436</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>472</v>
+        <v>437</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8728,13 +8740,13 @@
         <v>82</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>153</v>
+        <v>82</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>473</v>
+        <v>82</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>474</v>
+        <v>82</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>82</v>
@@ -8752,7 +8764,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>468</v>
+        <v>438</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8761,7 +8773,7 @@
         <v>93</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>475</v>
+        <v>105</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>106</v>
@@ -8773,10 +8785,10 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>107</v>
+        <v>439</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>476</v>
+        <v>440</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8787,50 +8799,52 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>477</v>
+        <v>441</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>477</v>
+        <v>441</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>478</v>
+        <v>82</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>257</v>
+        <v>173</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>479</v>
+        <v>442</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>480</v>
+        <v>443</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>481</v>
+        <v>309</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>482</v>
+        <v>444</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q54" s="2"/>
+      <c r="Q54" t="s" s="2">
+        <v>445</v>
+      </c>
       <c r="R54" t="s" s="2">
         <v>82</v>
       </c>
@@ -8850,13 +8864,13 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>153</v>
+        <v>248</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>483</v>
+        <v>446</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>484</v>
+        <v>447</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -8874,13 +8888,13 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>477</v>
+        <v>448</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>105</v>
@@ -8892,27 +8906,27 @@
         <v>82</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>485</v>
+        <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>486</v>
+        <v>449</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>487</v>
+        <v>450</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>488</v>
+        <v>82</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>489</v>
+        <v>451</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>489</v>
+        <v>451</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8920,10 +8934,10 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -8932,22 +8946,22 @@
         <v>82</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>490</v>
+        <v>109</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>491</v>
+        <v>452</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>492</v>
+        <v>453</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>493</v>
+        <v>309</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>494</v>
+        <v>454</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8957,7 +8971,7 @@
         <v>82</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>82</v>
+        <v>455</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>82</v>
@@ -8996,13 +9010,13 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>489</v>
+        <v>456</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>105</v>
@@ -9017,10 +9031,10 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>495</v>
+        <v>457</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>496</v>
+        <v>458</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -9031,10 +9045,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>497</v>
+        <v>459</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>497</v>
+        <v>459</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9054,21 +9068,23 @@
         <v>82</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>257</v>
+        <v>137</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>498</v>
+        <v>460</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>499</v>
+        <v>461</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>462</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
       </c>
@@ -9077,7 +9093,7 @@
         <v>82</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>82</v>
+        <v>464</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>82</v>
@@ -9092,13 +9108,13 @@
         <v>82</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>501</v>
+        <v>82</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>502</v>
+        <v>82</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>82</v>
@@ -9116,7 +9132,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>497</v>
+        <v>465</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9125,7 +9141,7 @@
         <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>105</v>
+        <v>466</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>106</v>
@@ -9134,27 +9150,27 @@
         <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>503</v>
+        <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>504</v>
+        <v>457</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>505</v>
+        <v>467</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>506</v>
+        <v>82</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>507</v>
+        <v>468</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>507</v>
+        <v>468</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9162,7 +9178,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>93</v>
@@ -9174,22 +9190,22 @@
         <v>82</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>257</v>
+        <v>173</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>508</v>
+        <v>469</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>509</v>
+        <v>470</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>510</v>
+        <v>471</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>511</v>
+        <v>472</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -9214,13 +9230,13 @@
         <v>82</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>512</v>
+        <v>82</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>513</v>
+        <v>82</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
@@ -9238,7 +9254,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>507</v>
+        <v>473</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9259,10 +9275,10 @@
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>514</v>
+        <v>457</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>515</v>
+        <v>474</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -9273,10 +9289,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>516</v>
+        <v>475</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>516</v>
+        <v>475</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9290,7 +9306,7 @@
         <v>93</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>82</v>
@@ -9299,18 +9315,20 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>517</v>
+        <v>257</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>518</v>
+        <v>476</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>519</v>
+        <v>477</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="O58" s="2"/>
+        <v>478</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>479</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
       </c>
@@ -9334,13 +9352,13 @@
         <v>82</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>82</v>
+        <v>153</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>82</v>
+        <v>480</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>82</v>
+        <v>481</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
@@ -9358,7 +9376,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>516</v>
+        <v>475</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9367,47 +9385,47 @@
         <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>105</v>
+        <v>482</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>230</v>
+        <v>106</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>521</v>
+        <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>522</v>
+        <v>107</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>523</v>
+        <v>483</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>524</v>
+        <v>82</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>525</v>
+        <v>484</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>525</v>
+        <v>484</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>82</v>
+        <v>485</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>82</v>
@@ -9419,18 +9437,20 @@
         <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>526</v>
+        <v>257</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>527</v>
+        <v>486</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>528</v>
+        <v>487</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>488</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>489</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
       </c>
@@ -9454,13 +9474,13 @@
         <v>82</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>82</v>
+        <v>153</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>82</v>
+        <v>490</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>82</v>
+        <v>491</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9478,45 +9498,45 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>525</v>
+        <v>484</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>230</v>
+        <v>106</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>530</v>
+        <v>492</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>531</v>
+        <v>493</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>532</v>
+        <v>494</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>533</v>
+        <v>495</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>534</v>
+        <v>496</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>534</v>
+        <v>496</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9539,19 +9559,19 @@
         <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>535</v>
+        <v>497</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>536</v>
+        <v>498</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>537</v>
+        <v>499</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>538</v>
+        <v>500</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>539</v>
+        <v>501</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9600,7 +9620,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>534</v>
+        <v>496</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9612,7 +9632,7 @@
         <v>105</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>540</v>
+        <v>106</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
@@ -9621,10 +9641,10 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>541</v>
+        <v>502</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>542</v>
+        <v>503</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9635,10 +9655,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>543</v>
+        <v>504</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>543</v>
+        <v>504</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9661,15 +9681,17 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>109</v>
+        <v>257</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>110</v>
+        <v>505</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>506</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>507</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9694,13 +9716,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>82</v>
+        <v>508</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>82</v>
+        <v>509</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9718,7 +9740,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>112</v>
+        <v>504</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9727,47 +9749,47 @@
         <v>93</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>82</v>
+        <v>510</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>82</v>
+        <v>511</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>113</v>
+        <v>512</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>82</v>
+        <v>513</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>544</v>
+        <v>514</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>544</v>
+        <v>514</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -9779,18 +9801,20 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>116</v>
+        <v>257</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>117</v>
+        <v>515</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>118</v>
+        <v>516</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>517</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>518</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9814,43 +9838,43 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>82</v>
+        <v>519</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>82</v>
+        <v>520</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>123</v>
+        <v>514</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>82</v>
@@ -9859,10 +9883,10 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>82</v>
+        <v>521</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>107</v>
+        <v>522</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9873,46 +9897,44 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>545</v>
+        <v>523</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>545</v>
+        <v>523</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>546</v>
+        <v>82</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>116</v>
+        <v>524</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>547</v>
+        <v>525</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>548</v>
+        <v>526</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>527</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
@@ -9960,45 +9982,45 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>549</v>
+        <v>523</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>124</v>
+        <v>230</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>82</v>
+        <v>528</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>82</v>
+        <v>529</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>107</v>
+        <v>530</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>82</v>
+        <v>531</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>550</v>
+        <v>532</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>550</v>
+        <v>532</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10021,16 +10043,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>551</v>
+        <v>533</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>552</v>
+        <v>534</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>554</v>
+        <v>536</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10080,7 +10102,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>550</v>
+        <v>532</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10089,36 +10111,36 @@
         <v>93</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>555</v>
+        <v>105</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>556</v>
+        <v>230</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>82</v>
+        <v>537</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>557</v>
+        <v>538</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>558</v>
+        <v>539</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>82</v>
+        <v>540</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>559</v>
+        <v>541</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>559</v>
+        <v>541</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10129,7 +10151,7 @@
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>82</v>
@@ -10141,18 +10163,20 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>560</v>
+        <v>543</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>561</v>
+        <v>544</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>545</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>546</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
@@ -10200,19 +10224,19 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>559</v>
+        <v>541</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>555</v>
+        <v>105</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>82</v>
@@ -10221,10 +10245,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>562</v>
+        <v>549</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10235,10 +10259,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>563</v>
+        <v>550</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>563</v>
+        <v>550</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10261,20 +10285,16 @@
         <v>82</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>257</v>
+        <v>109</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>564</v>
+        <v>110</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>567</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>82</v>
       </c>
@@ -10298,13 +10318,13 @@
         <v>82</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>568</v>
+        <v>82</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>569</v>
+        <v>82</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>82</v>
@@ -10322,7 +10342,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>563</v>
+        <v>112</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10331,22 +10351,22 @@
         <v>93</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>570</v>
+        <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>571</v>
+        <v>82</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>487</v>
+        <v>113</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10357,14 +10377,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>572</v>
+        <v>551</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>572</v>
+        <v>551</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10383,20 +10403,18 @@
         <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>257</v>
+        <v>116</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>573</v>
+        <v>117</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>574</v>
+        <v>118</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>576</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>82</v>
       </c>
@@ -10420,31 +10438,31 @@
         <v>82</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>577</v>
+        <v>82</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>578</v>
+        <v>82</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>572</v>
+        <v>123</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10456,19 +10474,19 @@
         <v>105</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>570</v>
+        <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>571</v>
+        <v>82</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>487</v>
+        <v>107</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10479,45 +10497,45 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>579</v>
+        <v>552</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>579</v>
+        <v>552</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>82</v>
+        <v>553</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>580</v>
+        <v>116</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>581</v>
+        <v>554</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>582</v>
+        <v>555</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>583</v>
+        <v>119</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>584</v>
+        <v>212</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10566,19 +10584,19 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>579</v>
+        <v>556</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>585</v>
+        <v>124</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>82</v>
@@ -10587,10 +10605,10 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>586</v>
+        <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>587</v>
+        <v>107</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10601,10 +10619,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>588</v>
+        <v>557</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>588</v>
+        <v>557</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10627,16 +10645,16 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>109</v>
+        <v>558</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>589</v>
+        <v>559</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>590</v>
+        <v>560</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>309</v>
+        <v>561</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10686,7 +10704,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>588</v>
+        <v>557</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10695,10 +10713,10 @@
         <v>93</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>105</v>
+        <v>562</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>106</v>
+        <v>563</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>82</v>
@@ -10707,10 +10725,10 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>591</v>
+        <v>565</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10721,10 +10739,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>592</v>
+        <v>566</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>592</v>
+        <v>566</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10735,7 +10753,7 @@
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>82</v>
@@ -10744,19 +10762,19 @@
         <v>82</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>593</v>
+        <v>558</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>594</v>
+        <v>567</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>595</v>
+        <v>568</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>596</v>
+        <v>561</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10806,19 +10824,19 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>592</v>
+        <v>566</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>105</v>
+        <v>562</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>230</v>
+        <v>563</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>82</v>
@@ -10827,10 +10845,10 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>597</v>
+        <v>564</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>598</v>
+        <v>569</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10841,10 +10859,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>599</v>
+        <v>570</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>599</v>
+        <v>570</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10855,7 +10873,7 @@
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>82</v>
@@ -10864,21 +10882,23 @@
         <v>82</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>600</v>
+        <v>257</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>601</v>
+        <v>571</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>602</v>
+        <v>572</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="O71" s="2"/>
+        <v>573</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>574</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
       </c>
@@ -10902,13 +10922,13 @@
         <v>82</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>82</v>
+        <v>575</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>82</v>
+        <v>576</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>82</v>
@@ -10926,31 +10946,31 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>599</v>
+        <v>570</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>230</v>
+        <v>106</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>82</v>
+        <v>577</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>597</v>
+        <v>578</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>604</v>
+        <v>494</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -10961,10 +10981,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>605</v>
+        <v>579</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>605</v>
+        <v>579</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10978,28 +10998,28 @@
         <v>81</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>535</v>
+        <v>257</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>606</v>
+        <v>580</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>606</v>
+        <v>581</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>607</v>
+        <v>582</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>608</v>
+        <v>583</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>82</v>
@@ -11024,13 +11044,13 @@
         <v>82</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>82</v>
+        <v>584</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>82</v>
+        <v>585</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>82</v>
@@ -11048,7 +11068,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>605</v>
+        <v>579</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11060,19 +11080,19 @@
         <v>105</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>609</v>
+        <v>106</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>82</v>
+        <v>577</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>610</v>
+        <v>578</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>611</v>
+        <v>494</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -11083,10 +11103,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>612</v>
+        <v>586</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>612</v>
+        <v>586</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11109,16 +11129,20 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>109</v>
+        <v>587</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>110</v>
+        <v>588</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
+        <v>589</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>591</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>82</v>
       </c>
@@ -11166,7 +11190,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>112</v>
+        <v>586</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11175,10 +11199,10 @@
         <v>93</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>82</v>
+        <v>592</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>82</v>
@@ -11187,10 +11211,10 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>82</v>
+        <v>593</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>113</v>
+        <v>594</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11201,21 +11225,21 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>613</v>
+        <v>595</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>613</v>
+        <v>595</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>82</v>
@@ -11227,16 +11251,16 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>117</v>
+        <v>596</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>118</v>
+        <v>597</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>119</v>
+        <v>309</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11274,31 +11298,31 @@
         <v>82</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>123</v>
+        <v>595</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>82</v>
@@ -11307,10 +11331,10 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>82</v>
+        <v>564</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>107</v>
+        <v>598</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11321,14 +11345,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>614</v>
+        <v>599</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>614</v>
+        <v>599</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>546</v>
+        <v>82</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -11341,26 +11365,24 @@
         <v>82</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J75" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>116</v>
+        <v>600</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>547</v>
+        <v>601</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>548</v>
+        <v>602</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>603</v>
+      </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>82</v>
       </c>
@@ -11408,7 +11430,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>549</v>
+        <v>599</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11420,7 +11442,7 @@
         <v>105</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>124</v>
+        <v>230</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
@@ -11429,10 +11451,10 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>82</v>
+        <v>604</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>107</v>
+        <v>605</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11443,10 +11465,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11454,13 +11476,13 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>82</v>
@@ -11469,20 +11491,18 @@
         <v>94</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>257</v>
+        <v>607</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>619</v>
-      </c>
+        <v>610</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>82</v>
       </c>
@@ -11506,13 +11526,13 @@
         <v>82</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>153</v>
+        <v>82</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>349</v>
+        <v>82</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>350</v>
+        <v>82</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>82</v>
@@ -11530,34 +11550,34 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>106</v>
+        <v>230</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>620</v>
+        <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>353</v>
+        <v>604</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>354</v>
+        <v>611</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>355</v>
+        <v>82</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>82</v>
@@ -11565,10 +11585,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11579,7 +11599,7 @@
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>94</v>
@@ -11591,19 +11611,19 @@
         <v>94</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>622</v>
+        <v>542</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>623</v>
+        <v>613</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>417</v>
+        <v>615</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -11628,13 +11648,13 @@
         <v>82</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>248</v>
+        <v>82</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>626</v>
+        <v>82</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>627</v>
+        <v>82</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>82</v>
@@ -11652,45 +11672,45 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>628</v>
+        <v>105</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>106</v>
+        <v>616</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>629</v>
+        <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>420</v>
+        <v>617</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>421</v>
+        <v>618</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>422</v>
+        <v>82</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>630</v>
+        <v>619</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>630</v>
+        <v>619</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11704,7 +11724,7 @@
         <v>93</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>82</v>
@@ -11713,20 +11733,16 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>257</v>
+        <v>109</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>631</v>
+        <v>110</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>472</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>82</v>
       </c>
@@ -11750,13 +11766,13 @@
         <v>82</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>153</v>
+        <v>82</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>473</v>
+        <v>82</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>474</v>
+        <v>82</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>82</v>
@@ -11774,7 +11790,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>630</v>
+        <v>112</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11783,10 +11799,10 @@
         <v>93</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>634</v>
+        <v>82</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>82</v>
@@ -11795,10 +11811,10 @@
         <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>476</v>
+        <v>113</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11809,14 +11825,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>635</v>
+        <v>620</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>635</v>
+        <v>620</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>478</v>
+        <v>115</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11835,20 +11851,18 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>257</v>
+        <v>116</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>479</v>
+        <v>117</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>480</v>
+        <v>118</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>482</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>82</v>
       </c>
@@ -11872,31 +11886,31 @@
         <v>82</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>153</v>
+        <v>82</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>483</v>
+        <v>82</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>484</v>
+        <v>82</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>635</v>
+        <v>123</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11908,37 +11922,37 @@
         <v>105</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>485</v>
+        <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>486</v>
+        <v>82</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>487</v>
+        <v>107</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>488</v>
+        <v>82</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>636</v>
+        <v>621</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>636</v>
+        <v>621</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>82</v>
+        <v>553</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11951,25 +11965,25 @@
         <v>82</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>637</v>
+        <v>554</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>638</v>
+        <v>555</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>538</v>
+        <v>119</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>539</v>
+        <v>212</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -12018,7 +12032,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>636</v>
+        <v>556</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12027,10 +12041,10 @@
         <v>81</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>82</v>
@@ -12039,20 +12053,630 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>541</v>
+        <v>82</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>542</v>
+        <v>107</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP80" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="P81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AO81" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AP81" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="82" hidden="true">
+      <c r="A82" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="P82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AO82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP82" t="s" s="2">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="83" hidden="true">
+      <c r="A83" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="P83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AO83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP83" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" hidden="true">
+      <c r="A84" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="P84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AO84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP84" t="s" s="2">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="P85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AO85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP85" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP80">
+  <autoFilter ref="A1:AP85">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12062,7 +12686,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI79">
+  <conditionalFormatting sqref="A2:AI84">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T14:34:19+00:00</t>
+    <t>2023-12-12T16:43:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T16:43:39+00:00</t>
+    <t>2023-12-13T09:56:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
